--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486947_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486947_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.9544</v>
+        <v>9.67</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8929</v>
+        <v>6.2527</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0616</v>
+        <v>3.4173</v>
       </c>
       <c r="G2" t="n">
         <v>6.3251</v>
@@ -610,13 +610,13 @@
         <v>2.8748</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9949</v>
+        <v>0.7206</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7673</v>
+        <v>0.5926</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2276</v>
+        <v>0.1281</v>
       </c>
       <c r="V2" t="n">
         <v>2.0082</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. PUIDET</t>
+          <t>K. CURFMAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.6718</v>
+        <v>6.2754</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7064</v>
+        <v>4.3999</v>
       </c>
       <c r="F3" t="n">
-        <v>3.9653</v>
+        <v>1.8755</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0709</v>
+        <v>4.8772</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5448</v>
+        <v>1.4888</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5261</v>
+        <v>3.3883</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8779</v>
+        <v>4.629</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2599</v>
+        <v>1.2882</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6181</v>
+        <v>3.3408</v>
       </c>
       <c r="M3" t="n">
-        <v>0.193</v>
+        <v>0.2482</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2849</v>
+        <v>0.2007</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.092</v>
+        <v>0.0475</v>
       </c>
       <c r="P3" t="n">
-        <v>2.2588</v>
+        <v>1.4374</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2053</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4641</v>
+        <v>1.4374</v>
       </c>
       <c r="S3" t="n">
-        <v>1.993</v>
+        <v>0.5502</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3829</v>
+        <v>0.12</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6101</v>
+        <v>0.4302</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3491</v>
+        <v>-0.5893</v>
       </c>
       <c r="W3" t="n">
         <v>-0.3491</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6982</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. CURFMAN</t>
+          <t>J. PUIDET</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.0829</v>
+        <v>5.0542</v>
       </c>
       <c r="E4" t="n">
-        <v>3.563</v>
+        <v>1.5631</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5198</v>
+        <v>3.4911</v>
       </c>
       <c r="G4" t="n">
-        <v>4.8772</v>
+        <v>1.0709</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4888</v>
+        <v>0.5448</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3883</v>
+        <v>0.5261</v>
       </c>
       <c r="J4" t="n">
-        <v>4.629</v>
+        <v>0.8779</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2882</v>
+        <v>0.2599</v>
       </c>
       <c r="L4" t="n">
-        <v>3.3408</v>
+        <v>0.6181</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2482</v>
+        <v>0.193</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2007</v>
+        <v>0.2849</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0475</v>
+        <v>-0.092</v>
       </c>
       <c r="P4" t="n">
-        <v>1.4374</v>
+        <v>2.2588</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.2053</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4374</v>
+        <v>2.4641</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6424</v>
+        <v>1.3754</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7169</v>
+        <v>1.2396</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0745</v>
+        <v>0.1358</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5893</v>
+        <v>0.3491</v>
       </c>
       <c r="W4" t="n">
         <v>-0.3491</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2402</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.5429</v>
+        <v>4.3089</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1872</v>
+        <v>2.8347</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3556</v>
+        <v>1.4742</v>
       </c>
       <c r="G5" t="n">
         <v>0.7166</v>
@@ -844,13 +844,13 @@
         <v>2.2588</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6209</v>
+        <v>1.387</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7936</v>
+        <v>1.4411</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1727</v>
+        <v>-0.0541</v>
       </c>
       <c r="V5" t="n">
         <v>1.1786</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.475</v>
+        <v>3.476</v>
       </c>
       <c r="E6" t="n">
-        <v>2.392</v>
+        <v>1.6597</v>
       </c>
       <c r="F6" t="n">
-        <v>2.083</v>
+        <v>1.8163</v>
       </c>
       <c r="G6" t="n">
         <v>2.5909</v>
@@ -922,13 +922,13 @@
         <v>1.0267</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2127</v>
+        <v>1.2137</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2203</v>
+        <v>0.488</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.7256</v>
       </c>
       <c r="V6" t="n">
         <v>0.6982</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. SANTANO BARTOLOME</t>
+          <t>A. BUTKO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5662</v>
+        <v>0.6647</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6548</v>
+        <v>0.5508</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0886</v>
+        <v>0.114</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1261</v>
+        <v>-0.7541</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6683</v>
+        <v>-0.12</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4579</v>
+        <v>-0.6341</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1047</v>
+        <v>-0.7518</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2759</v>
+        <v>-0.0939</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8288</v>
+        <v>-0.6579</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0214</v>
+        <v>-0.0023</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3923</v>
+        <v>-0.0261</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3709</v>
+        <v>0.0238</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8214</v>
+        <v>0.2053</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8214</v>
+        <v>0.2053</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7357</v>
+        <v>0.0349</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3098</v>
+        <v>0.1239</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4259</v>
+        <v>-0.0891</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.117</v>
+        <v>1.1786</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2402</v>
+        <v>1.1786</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.3573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. BUTKO</t>
+          <t>J. ORTEGA MORA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3509</v>
+        <v>0.4057</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2369</v>
+        <v>0.7625</v>
       </c>
       <c r="F8" t="n">
-        <v>0.114</v>
+        <v>-0.3568</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7541</v>
+        <v>0.18</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.12</v>
+        <v>-0.2304</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6341</v>
+        <v>0.4104</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7518</v>
+        <v>0.5456</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0939</v>
+        <v>0.0195</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6579</v>
+        <v>0.5261</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0023</v>
+        <v>-0.3656</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0261</v>
+        <v>-0.2498</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0238</v>
+        <v>-0.1157</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2053</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2053</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2789</v>
+        <v>0.2257</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1899</v>
+        <v>0.2169</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0891</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. ORTEGA MORA</t>
+          <t>J. SANTANO BARTOLOME</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1075</v>
+        <v>0.3274</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5533</v>
+        <v>1.4456</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4457</v>
+        <v>-1.1182</v>
       </c>
       <c r="G9" t="n">
-        <v>0.18</v>
+        <v>1.1261</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2304</v>
+        <v>0.6683</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4104</v>
+        <v>0.4579</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5456</v>
+        <v>1.1047</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0195</v>
+        <v>0.2759</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5261</v>
+        <v>0.8288</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3656</v>
+        <v>0.0214</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2498</v>
+        <v>0.3923</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1157</v>
+        <v>-0.3709</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.8214</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.8214</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0725</v>
+        <v>0.4969</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0077</v>
+        <v>0.1006</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.08019999999999999</v>
+        <v>0.3962</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.117</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. SIMEUNOVIC</t>
+          <t>A. MORENO TRUJILLO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1562</v>
+        <v>-1.1797</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1388</v>
+        <v>-1.5719</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9826</v>
+        <v>0.3921</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3732</v>
+        <v>-2.9014</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.294</v>
+        <v>-1.596</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9207</v>
+        <v>-1.3054</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0492</v>
+        <v>-2.6178</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3582</v>
+        <v>-1.6833</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4074</v>
+        <v>-0.9345</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4224</v>
+        <v>-0.2836</v>
       </c>
       <c r="N10" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.0873</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4866</v>
+        <v>-0.3709</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.4641</v>
+        <v>1.4374</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.1336</v>
+        <v>-0.2053</v>
       </c>
       <c r="R10" t="n">
-        <v>2.6694</v>
+        <v>1.6427</v>
       </c>
       <c r="S10" t="n">
-        <v>1.6811</v>
+        <v>1.1138</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7669</v>
+        <v>1.2513</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9142</v>
+        <v>-0.1374</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.8295</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1786</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. MORENO TRUJILLO</t>
+          <t>D. SIMEUNOVIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2909</v>
+        <v>-1.3118</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7423</v>
+        <v>-2.9683</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4514</v>
+        <v>1.6566</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.9014</v>
+        <v>-0.3732</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.596</v>
+        <v>-1.294</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3054</v>
+        <v>0.9207</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.6178</v>
+        <v>0.0492</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.6833</v>
+        <v>-1.3582</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.9345</v>
+        <v>1.4074</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2836</v>
+        <v>-0.4224</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0873</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3709</v>
+        <v>-0.4866</v>
       </c>
       <c r="P11" t="n">
-        <v>1.4374</v>
+        <v>-2.4641</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.2053</v>
+        <v>-5.1336</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6427</v>
+        <v>2.6694</v>
       </c>
       <c r="S11" t="n">
-        <v>1.0026</v>
+        <v>1.5255</v>
       </c>
       <c r="T11" t="n">
-        <v>1.0808</v>
+        <v>0.9374</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.07820000000000001</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.8295</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.8295</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4747</v>
+        <v>-2.8296</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9041</v>
+        <v>-0.5991</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3788</v>
+        <v>-2.2306</v>
       </c>
       <c r="G12" t="n">
         <v>-1.6181</v>
@@ -1390,13 +1390,13 @@
         <v>1.0267</v>
       </c>
       <c r="S12" t="n">
-        <v>2.7061</v>
+        <v>1.3511</v>
       </c>
       <c r="T12" t="n">
-        <v>2.9752</v>
+        <v>1.4721</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2692</v>
+        <v>-0.121</v>
       </c>
       <c r="V12" t="n">
         <v>-2.3573</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.0877</v>
+        <v>-3.7896</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.4473</v>
+        <v>-3.2381</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6404</v>
+        <v>-0.5515</v>
       </c>
       <c r="G13" t="n">
         <v>-1.7565</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2778</v>
+        <v>0.0203</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0581</v>
+        <v>0.1511</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2197</v>
+        <v>-0.1307</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>20.74210000000001</v>
+        <v>21.0716</v>
       </c>
       <c r="E14" t="n">
-        <v>10.7622</v>
+        <v>11.0916</v>
       </c>
       <c r="F14" t="n">
-        <v>9.979800000000001</v>
+        <v>9.979999999999997</v>
       </c>
       <c r="G14" t="n">
         <v>9.483499999999999</v>
@@ -1522,7 +1522,7 @@
         <v>11.7644</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7294</v>
+        <v>2.729399999999999</v>
       </c>
       <c r="L14" t="n">
         <v>9.0352</v>
@@ -1537,7 +1537,7 @@
         <v>-2.8929</v>
       </c>
       <c r="P14" t="n">
-        <v>2.053500000000001</v>
+        <v>2.0535</v>
       </c>
       <c r="Q14" t="n">
         <v>-14.374</v>
@@ -1546,13 +1546,13 @@
         <v>16.4273</v>
       </c>
       <c r="S14" t="n">
-        <v>9.685600000000001</v>
+        <v>10.0151</v>
       </c>
       <c r="T14" t="n">
-        <v>7.805000000000001</v>
+        <v>8.134600000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>1.8804</v>
+        <v>1.8805</v>
       </c>
       <c r="V14" t="n">
         <v>-0.4803999999999995</v>
@@ -1561,13 +1561,13 @@
         <v>5.5664</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.047000000000001</v>
+        <v>-6.047</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. ABDULSALAM</t>
+          <t>A. AKINWOLE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7653</v>
+        <v>2.7162</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3504</v>
+        <v>4.0554</v>
       </c>
       <c r="F15" t="n">
-        <v>3.4148</v>
+        <v>-1.3392</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.6077</v>
+        <v>4.211</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0606</v>
+        <v>1.9404</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5472</v>
+        <v>2.2706</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.1586</v>
+        <v>4.6097</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.5402</v>
+        <v>2.2946</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6183999999999999</v>
+        <v>2.3151</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5508999999999999</v>
+        <v>-0.3987</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4796</v>
+        <v>-0.3542</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0713</v>
+        <v>-0.0445</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4107</v>
+        <v>1.8481</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6427</v>
+        <v>1.8481</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5887</v>
+        <v>-1.4045</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5461</v>
+        <v>-0.5542</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0426</v>
+        <v>-0.8502</v>
       </c>
       <c r="V15" t="n">
-        <v>4.195</v>
+        <v>-1.9384</v>
       </c>
       <c r="W15" t="n">
-        <v>4.0164</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1787</v>
+        <v>-1.9384</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. AKINWOLE</t>
+          <t>M. ABDULSALAM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1409</v>
+        <v>2.6319</v>
       </c>
       <c r="E16" t="n">
-        <v>4.0554</v>
+        <v>-0.1726</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9146</v>
+        <v>2.8045</v>
       </c>
       <c r="G16" t="n">
-        <v>4.211</v>
+        <v>-1.6077</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9404</v>
+        <v>-1.0606</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2706</v>
+        <v>-0.5472</v>
       </c>
       <c r="J16" t="n">
-        <v>4.6097</v>
+        <v>-2.1586</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2946</v>
+        <v>-1.5402</v>
       </c>
       <c r="L16" t="n">
-        <v>2.3151</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3987</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3542</v>
+        <v>0.4796</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0445</v>
+        <v>0.0713</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8481</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8481</v>
+        <v>1.6427</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.9798</v>
+        <v>0.4553</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5542</v>
+        <v>0.0231</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.4256</v>
+        <v>0.4322</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.9384</v>
+        <v>4.195</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>4.0164</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.9384</v>
+        <v>0.1787</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. HENDERSON</t>
+          <t>E. ORTIZ TORRES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.101</v>
+        <v>0.5347</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.09229999999999999</v>
+        <v>1.8942</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-1.3595</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.605</v>
+        <v>0.0931</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2498</v>
+        <v>0.3375</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3552</v>
+        <v>-0.2445</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0395</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.474</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0395</v>
+        <v>0.0789</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6445</v>
+        <v>-0.4599</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2498</v>
+        <v>-0.1365</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3947</v>
+        <v>-0.3234</v>
       </c>
       <c r="P17" t="n">
-        <v>0.616</v>
+        <v>0.8214</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.616</v>
+        <v>0.8214</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.112</v>
+        <v>-0.1395</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1317</v>
+        <v>0.1626</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0198</v>
+        <v>-0.3021</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4947</v>
+        <v>0.1364</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0875</v>
+        <v>-0.7737000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5928</v>
+        <v>0.9101</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1445</v>
@@ -1858,13 +1858,13 @@
         <v>0.616</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9663</v>
+        <v>-0.3352</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.527</v>
+        <v>-0.2132</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4393</v>
+        <v>-0.122</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. ORTIZ TORRES</t>
+          <t>C. HENDERSON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6787</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4758</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1545</v>
+        <v>0.0209</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0931</v>
+        <v>-0.605</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3375</v>
+        <v>-0.2498</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2445</v>
+        <v>-0.3552</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.0395</v>
       </c>
       <c r="K19" t="n">
-        <v>0.474</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0789</v>
+        <v>0.0395</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4599</v>
+        <v>-0.6445</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1365</v>
+        <v>-0.2498</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3234</v>
+        <v>-0.3947</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8214</v>
+        <v>0.616</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8214</v>
+        <v>0.616</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3529</v>
+        <v>-0.0823</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2558</v>
+        <v>-0.1317</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0971</v>
+        <v>0.0494</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.4189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2986</v>
+        <v>-1.2113</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8132</v>
+        <v>1.604</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.1117</v>
+        <v>-2.8153</v>
       </c>
       <c r="G20" t="n">
         <v>-0.1393</v>
@@ -2014,13 +2014,13 @@
         <v>1.4374</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4878</v>
+        <v>-1.4006</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3566</v>
+        <v>-0.5658</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1312</v>
+        <v>-0.8348</v>
       </c>
       <c r="V20" t="n">
         <v>-1.1088</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0275</v>
+        <v>-1.44</v>
       </c>
       <c r="E21" t="n">
         <v>-1.3226</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7049</v>
+        <v>-0.1174</v>
       </c>
       <c r="G21" t="n">
         <v>3.1814</v>
@@ -2092,13 +2092,13 @@
         <v>1.8481</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.0568</v>
+        <v>-1.4693</v>
       </c>
       <c r="T21" t="n">
         <v>-0.4806</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.5762</v>
+        <v>-0.9887</v>
       </c>
       <c r="V21" t="n">
         <v>2.1868</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2369</v>
+        <v>-1.6406</v>
       </c>
       <c r="E22" t="n">
         <v>-2.7719</v>
       </c>
       <c r="F22" t="n">
-        <v>0.535</v>
+        <v>1.1313</v>
       </c>
       <c r="G22" t="n">
         <v>-1.6698</v>
@@ -2170,13 +2170,13 @@
         <v>1.4374</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0476</v>
+        <v>-0.4513</v>
       </c>
       <c r="T22" t="n">
         <v>0.1122</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1598</v>
+        <v>-0.5636</v>
       </c>
       <c r="V22" t="n">
         <v>0.0698</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. NVE MALEVA</t>
+          <t>M. ALVAREZ PUERTAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.8818</v>
+        <v>-4.5513</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4123</v>
+        <v>-2.3374</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.4696</v>
+        <v>-2.2139</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.2937</v>
+        <v>-3.8636</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.3787</v>
+        <v>-0.4642</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.9151</v>
+        <v>-3.3994</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.9425</v>
+        <v>-0.9889</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.0214</v>
+        <v>0.3927</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0789</v>
+        <v>-1.3817</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.3512</v>
+        <v>-2.8747</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3572</v>
+        <v>-0.8569</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.994</v>
+        <v>-2.0177</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.8214</v>
+        <v>0.4107</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="S23" t="n">
-        <v>1.2189</v>
+        <v>-1.0984</v>
       </c>
       <c r="T23" t="n">
-        <v>1.8013</v>
+        <v>-0.3217</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5824</v>
+        <v>-0.7766</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.9856</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.2177</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.7679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. ALVAREZ PUERTAS</t>
+          <t>J. NVE MALEVA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.6217</v>
+        <v>-6.0988</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0696</v>
+        <v>-2.7721</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.5521</v>
+        <v>-3.3267</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.8636</v>
+        <v>-3.2937</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4642</v>
+        <v>-1.3787</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.3994</v>
+        <v>-1.9151</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9889</v>
+        <v>-0.9425</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3927</v>
+        <v>-1.0214</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.3817</v>
+        <v>0.0789</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.8747</v>
+        <v>-2.3512</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8569</v>
+        <v>-0.3572</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.0177</v>
+        <v>-1.994</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4107</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4374</v>
+        <v>1.2321</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.1688</v>
+        <v>0.0019</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.054</v>
+        <v>0.4415</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.1149</v>
+        <v>-0.4396</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-1.9856</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.2177</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-9.3073</v>
+        <v>-8.261200000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.9186</v>
+        <v>-7.291</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.3887</v>
+        <v>-0.9703000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-5.6453</v>
@@ -2404,13 +2404,13 @@
         <v>1.4374</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3211</v>
+        <v>-0.2751</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9804</v>
+        <v>-0.3527</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3408</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6982</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-20.742</v>
+        <v>-17.2554</v>
       </c>
       <c r="E26" t="n">
         <v>-9.98</v>
       </c>
       <c r="F26" t="n">
-        <v>-10.7622</v>
+        <v>-7.2755</v>
       </c>
       <c r="G26" t="n">
         <v>-9.4834</v>
@@ -2455,7 +2455,7 @@
         <v>-6.142300000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>2.281099999999999</v>
+        <v>2.2811</v>
       </c>
       <c r="K26" t="n">
         <v>-0.6120000000000003</v>
@@ -2482,13 +2482,13 @@
         <v>14.374</v>
       </c>
       <c r="S26" t="n">
-        <v>-9.685499999999999</v>
+        <v>-6.199000000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.8807</v>
+        <v>-1.8805</v>
       </c>
       <c r="U26" t="n">
-        <v>-7.8049</v>
+        <v>-4.318299999999999</v>
       </c>
       <c r="V26" t="n">
         <v>0.4804</v>
@@ -2497,7 +2497,7 @@
         <v>6.047000000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-5.5666</v>
+        <v>-5.566599999999999</v>
       </c>
     </row>
   </sheetData>
